--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.89519304473195</v>
+        <v>7.782968869768943</v>
       </c>
       <c r="D2" t="n">
-        <v>2.437240732358297</v>
+        <v>0.3960516190082232</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F2" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.50756020645404</v>
+        <v>11.13247853354878</v>
       </c>
       <c r="D3" t="n">
-        <v>68.40614640807622</v>
+        <v>11.11599879131239</v>
       </c>
       <c r="E3" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F3" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.14454476776717</v>
+        <v>8.473488524762166</v>
       </c>
       <c r="D4" t="n">
-        <v>52.22059134421677</v>
+        <v>8.485846093435226</v>
       </c>
       <c r="E4" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F4" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.45099693908785</v>
+        <v>4.623287002601776</v>
       </c>
       <c r="D5" t="n">
-        <v>27.57778234529178</v>
+        <v>4.481389631109914</v>
       </c>
       <c r="E5" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F5" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.20406703778232</v>
+        <v>3.283160893639626</v>
       </c>
       <c r="D6" t="n">
-        <v>19.67441145704392</v>
+        <v>3.197091861769637</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F6" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.9196993936826</v>
+        <v>3.074451151473423</v>
       </c>
       <c r="D7" t="n">
-        <v>19.13328163648519</v>
+        <v>3.109158265928843</v>
       </c>
       <c r="E7" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F7" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.62038346154603</v>
+        <v>7.413312312501231</v>
       </c>
       <c r="D8" t="n">
-        <v>45.23164128881596</v>
+        <v>7.350141709432594</v>
       </c>
       <c r="E8" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F8" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>4.147471970580827</v>
+        <v>0.6739641952193843</v>
       </c>
       <c r="D9" t="n">
-        <v>5.311449749279936</v>
+        <v>0.8631105842579897</v>
       </c>
       <c r="E9" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F9" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.62308393980305</v>
+        <v>8.713751140217996</v>
       </c>
       <c r="D10" t="n">
-        <v>53.16458960945693</v>
+        <v>8.639245811536751</v>
       </c>
       <c r="E10" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F10" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.202137109224539</v>
+        <v>1.332847280248988</v>
       </c>
       <c r="D11" t="n">
-        <v>9.266322045211769</v>
+        <v>1.505777332346913</v>
       </c>
       <c r="E11" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F11" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.14700731735556</v>
+        <v>4.736388689070279</v>
       </c>
       <c r="D12" t="n">
-        <v>28.25929920734875</v>
+        <v>4.592136121194171</v>
       </c>
       <c r="E12" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F12" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.5471227696352</v>
+        <v>4.63890745006572</v>
       </c>
       <c r="D13" t="n">
-        <v>27.9070032206242</v>
+        <v>4.534888023351432</v>
       </c>
       <c r="E13" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F13" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.67907145961146</v>
+        <v>5.635349112186862</v>
       </c>
       <c r="D14" t="n">
-        <v>35.06342766926277</v>
+        <v>5.697806996255199</v>
       </c>
       <c r="E14" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F14" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.76233682436637</v>
+        <v>6.136379733959536</v>
       </c>
       <c r="D15" t="n">
-        <v>37.39276996669271</v>
+        <v>6.076325119587565</v>
       </c>
       <c r="E15" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F15" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.29182928697713</v>
+        <v>5.247422259133783</v>
       </c>
       <c r="D16" t="n">
-        <v>29.81860054392592</v>
+        <v>4.845522588387961</v>
       </c>
       <c r="E16" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F16" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.47300328851857</v>
+        <v>6.901863034384268</v>
       </c>
       <c r="D17" t="n">
-        <v>42.24657594709154</v>
+        <v>6.865068591402376</v>
       </c>
       <c r="E17" t="n">
-        <v>16.53855597082674</v>
+        <v>2.687515345259345</v>
       </c>
       <c r="F17" t="n">
-        <v>17.62704729072565</v>
+        <v>2.864395184742919</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
